--- a/_passpq/inputs/PEQ_L2K_YearPlan_2026-27.xlsx
+++ b/_passpq/inputs/PEQ_L2K_YearPlan_2026-27.xlsx
@@ -6104,7 +6104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6146,10 +6146,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>0.6667</v>
       </c>
       <c r="B2" t="n">
-        <v>76</v>
+        <v>25.33</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6166,19 +6166,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>7.666666666666667</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>0.6667</v>
       </c>
       <c r="B3" t="n">
-        <v>76</v>
+        <v>25.33</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -6199,15 +6199,15 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>57.66666666666666</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>0.6667</v>
       </c>
       <c r="B4" t="n">
-        <v>76</v>
+        <v>25.33</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -6228,15 +6228,15 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>57</v>
+        <v>107.6666666666667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>0.6667</v>
       </c>
       <c r="B5" t="n">
-        <v>76</v>
+        <v>25.33</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -6253,19 +6253,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>8.666666666666666</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>0.6667</v>
       </c>
       <c r="B6" t="n">
-        <v>76</v>
+        <v>25.33</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -6286,15 +6286,15 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>53.66666666666666</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>0.6667</v>
       </c>
       <c r="B7" t="n">
-        <v>76</v>
+        <v>25.33</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -6315,15 +6315,15 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>57</v>
+        <v>107.6666666666667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>0.6667</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>25.33</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -6340,19 +6340,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>0.6667</v>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>25.33</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -6369,19 +6369,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>46.66666666666666</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>0.6667</v>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>25.33</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -6402,15 +6402,15 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>44</v>
+        <v>94.66666666666667</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>1.3333</v>
       </c>
       <c r="B11" t="n">
-        <v>114</v>
+        <v>50.67</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -6436,10 +6436,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>1.3333</v>
       </c>
       <c r="B12" t="n">
-        <v>114</v>
+        <v>50.67</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -6456,19 +6456,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>32.33333333333334</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>1.3333</v>
       </c>
       <c r="B13" t="n">
-        <v>114</v>
+        <v>50.67</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -6489,15 +6489,15 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>19</v>
+        <v>82.33333333333333</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3</v>
+        <v>1.3333</v>
       </c>
       <c r="B14" t="n">
-        <v>114</v>
+        <v>50.67</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -6523,10 +6523,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>1.3333</v>
       </c>
       <c r="B15" t="n">
-        <v>114</v>
+        <v>50.67</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -6543,19 +6543,19 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>28.33333333333333</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>1.3333</v>
       </c>
       <c r="B16" t="n">
-        <v>114</v>
+        <v>50.67</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -6576,15 +6576,15 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>19</v>
+        <v>82.33333333333333</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>1.3333</v>
       </c>
       <c r="B17" t="n">
-        <v>114</v>
+        <v>50.67</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>1.3333</v>
       </c>
       <c r="B18" t="n">
-        <v>114</v>
+        <v>50.67</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -6630,19 +6630,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>21.33333333333333</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>1.3333</v>
       </c>
       <c r="B19" t="n">
-        <v>114</v>
+        <v>50.67</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -6663,15 +6663,15 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>69.33333333333333</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="B20" t="n">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -6697,10 +6697,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="B21" t="n">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -6717,19 +6717,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="B22" t="n">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -6746,19 +6746,19 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="B23" t="n">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -6784,10 +6784,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="B24" t="n">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -6804,19 +6804,19 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="B25" t="n">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -6833,19 +6833,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="B26" t="n">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -6871,10 +6871,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="B27" t="n">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -6900,10 +6900,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="B28" t="n">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -6920,19 +6920,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4</v>
+        <v>2.6667</v>
       </c>
       <c r="B29" t="n">
-        <v>152</v>
+        <v>101.33</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -6958,10 +6958,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4</v>
+        <v>2.6667</v>
       </c>
       <c r="B30" t="n">
-        <v>152</v>
+        <v>101.33</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -6987,10 +6987,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4</v>
+        <v>2.6667</v>
       </c>
       <c r="B31" t="n">
-        <v>152</v>
+        <v>101.33</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -7007,19 +7007,19 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>31.66666666666667</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>4</v>
+        <v>2.6667</v>
       </c>
       <c r="B32" t="n">
-        <v>152</v>
+        <v>101.33</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -7045,10 +7045,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>4</v>
+        <v>2.6667</v>
       </c>
       <c r="B33" t="n">
-        <v>152</v>
+        <v>101.33</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -7074,10 +7074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>4</v>
+        <v>2.6667</v>
       </c>
       <c r="B34" t="n">
-        <v>152</v>
+        <v>101.33</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -7094,19 +7094,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>31.66666666666667</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4</v>
+        <v>2.6667</v>
       </c>
       <c r="B35" t="n">
-        <v>152</v>
+        <v>101.33</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -7132,10 +7132,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4</v>
+        <v>2.6667</v>
       </c>
       <c r="B36" t="n">
-        <v>152</v>
+        <v>101.33</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -7161,10 +7161,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>4</v>
+        <v>2.6667</v>
       </c>
       <c r="B37" t="n">
-        <v>152</v>
+        <v>101.33</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -7181,10 +7181,1054 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>18.66666666666667</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3.3333</v>
+      </c>
+      <c r="B38" t="n">
+        <v>126.67</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Entry Level Award</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>40</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="G37" t="n">
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>3.3333</v>
+      </c>
+      <c r="B39" t="n">
+        <v>126.67</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Entry Level Extended Award</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>90</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>3.3333</v>
+      </c>
+      <c r="B40" t="n">
+        <v>126.67</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Entry Level Certificate</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>140</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>6.333333333333333</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>3.3333</v>
+      </c>
+      <c r="B41" t="n">
+        <v>126.67</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Level 1 Award</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>36</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>3.3333</v>
+      </c>
+      <c r="B42" t="n">
+        <v>126.67</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Level 1 Extended Award</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>81</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>3.3333</v>
+      </c>
+      <c r="B43" t="n">
+        <v>126.67</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Level 1 Certificate</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>135</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>6.333333333333333</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>3.3333</v>
+      </c>
+      <c r="B44" t="n">
+        <v>126.67</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Level 2 Award</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>32</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>3.3333</v>
+      </c>
+      <c r="B45" t="n">
+        <v>126.67</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Level 2 Extended Award</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>72</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>3.3333</v>
+      </c>
+      <c r="B46" t="n">
+        <v>126.67</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Level 2 Certificate</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>120</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="B47" t="n">
+        <v>133</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Entry Level Award</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>40</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="B48" t="n">
+        <v>133</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Entry Level Extended Award</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>90</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="B49" t="n">
+        <v>133</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Entry Level Certificate</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>140</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="B50" t="n">
+        <v>133</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Level 1 Award</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>36</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="B51" t="n">
+        <v>133</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Level 1 Extended Award</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>81</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="B52" t="n">
+        <v>133</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Level 1 Certificate</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>135</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="B53" t="n">
+        <v>133</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Level 2 Award</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>32</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="B54" t="n">
+        <v>133</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Level 2 Extended Award</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>72</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="B55" t="n">
+        <v>133</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Level 2 Certificate</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>120</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>4</v>
+      </c>
+      <c r="B56" t="n">
+        <v>152</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Entry Level Award</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>40</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B57" t="n">
+        <v>152</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Entry Level Extended Award</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>90</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>4</v>
+      </c>
+      <c r="B58" t="n">
+        <v>152</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Entry Level Certificate</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>140</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>4</v>
+      </c>
+      <c r="B59" t="n">
+        <v>152</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Level 1 Award</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>36</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>4</v>
+      </c>
+      <c r="B60" t="n">
+        <v>152</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Level 1 Extended Award</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>81</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>4</v>
+      </c>
+      <c r="B61" t="n">
+        <v>152</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Level 1 Certificate</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>135</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>4</v>
+      </c>
+      <c r="B62" t="n">
+        <v>152</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Level 2 Award</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>32</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>4</v>
+      </c>
+      <c r="B63" t="n">
+        <v>152</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Level 2 Extended Award</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>72</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>4</v>
+      </c>
+      <c r="B64" t="n">
+        <v>152</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Level 2 Certificate</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>120</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4.6667</v>
+      </c>
+      <c r="B65" t="n">
+        <v>177.33</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Entry Level Award</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>40</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>4.6667</v>
+      </c>
+      <c r="B66" t="n">
+        <v>177.33</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Entry Level Extended Award</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>90</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>4.6667</v>
+      </c>
+      <c r="B67" t="n">
+        <v>177.33</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Entry Level Certificate</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>140</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>4.6667</v>
+      </c>
+      <c r="B68" t="n">
+        <v>177.33</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Level 1 Award</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>36</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>4.6667</v>
+      </c>
+      <c r="B69" t="n">
+        <v>177.33</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Level 1 Extended Award</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>81</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>4.6667</v>
+      </c>
+      <c r="B70" t="n">
+        <v>177.33</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Level 1 Certificate</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>135</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>4.6667</v>
+      </c>
+      <c r="B71" t="n">
+        <v>177.33</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Level 2 Award</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>32</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>4.6667</v>
+      </c>
+      <c r="B72" t="n">
+        <v>177.33</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Level 2 Extended Award</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>72</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>4.6667</v>
+      </c>
+      <c r="B73" t="n">
+        <v>177.33</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Level 2 Certificate</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>120</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
         <v>0</v>
       </c>
     </row>

--- a/_passpq/inputs/PEQ_L2K_YearPlan_2026-27.xlsx
+++ b/_passpq/inputs/PEQ_L2K_YearPlan_2026-27.xlsx
@@ -8270,7 +8270,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L1 Certificate = 14 credits while the six L1 units sum to 15. DEFAULT: teach and evidence all six L1 units (15 credits - spec s5.1 permits exceeding the 14 minimum; all credits at level). Where a claim of exactly 14 is preferred, or a pupil is stretched by L1 Thinking (the largest E3-to-L1 step: assumptions + primary/secondary sources), the NAMED default combination is the five other L1 units (12 cr at L1) + ThSkE3 (2 cr adjacent) = 14 cr, min-11-at-level and max-3-below both satisfied - the only exact-14 arithmetic. Confirm the preferred claim shape with ASDAN at names-confirmation (QUESTIONS_FOR_CHERYL).</t>
+          <t>DECIDED (centre orchestration, PEQ-YEAR-1 s3). The L1 Certificate is 14 credits while the six L1 units sum to 15. THE CENTRE TEACHES AND EVIDENCES ALL SIX L1 UNITS - 15 credits, every one at level; spec s5.1 permits exceeding the 14 minimum. This is a choice already made, not an open question. The fallback, if a pupil is stretched by L1 Thinking (the largest E3-to-L1 step: assumptions + primary/secondary sources) or an exact-14 claim is later preferred, is the five other L1 units (12 cr at L1) + ThSkE3 (2 cr adjacent) = 14 - the only exact-14 arithmetic, with min-11-at-level and max-3-below both satisfied. Which shape is CLAIMED is stated to ASDAN at names-confirmation, ~4 weeks before EQA sampling; that is a normal step in the EQA cycle, not a decision still to be taken.</t>
         </is>
       </c>
     </row>

--- a/_passpq/inputs/PEQ_L2K_YearPlan_2026-27.xlsx
+++ b/_passpq/inputs/PEQ_L2K_YearPlan_2026-27.xlsx
@@ -525,11 +525,11 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3">
@@ -570,11 +570,11 @@
         <v>50</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4">
@@ -615,11 +615,11 @@
         <v>50</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5">
@@ -660,11 +660,11 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6">
@@ -705,11 +705,11 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7">
@@ -750,11 +750,11 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8">
@@ -795,11 +795,11 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9">
@@ -840,11 +840,11 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -885,11 +885,11 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11">
@@ -930,11 +930,11 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -975,11 +975,11 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13">
@@ -1020,11 +1020,11 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14">
@@ -1061,11 +1061,11 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15">
@@ -1102,11 +1102,11 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16">
@@ -1143,11 +1143,11 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17">
@@ -1184,11 +1184,11 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18">
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1225,15 +1225,11 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>40 Com</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19">
@@ -1252,7 +1248,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1270,15 +1266,11 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>40 Com</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20">
@@ -1315,11 +1307,11 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21">
@@ -1356,11 +1348,11 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22">
@@ -1397,11 +1389,11 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="23">
@@ -1438,11 +1430,11 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24">
@@ -1479,11 +1471,11 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="25">
@@ -1520,11 +1512,11 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26">
@@ -1561,11 +1553,11 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27">
@@ -1602,11 +1594,11 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28">
@@ -1640,18 +1632,14 @@
         <v>170</v>
       </c>
       <c r="J28" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>60 Wellb</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="29">
@@ -1685,18 +1673,14 @@
         <v>170</v>
       </c>
       <c r="J29" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>60 Wellb</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30">
@@ -1730,18 +1714,14 @@
         <v>170</v>
       </c>
       <c r="J30" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>60 Wellb</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="31">
@@ -1775,18 +1755,14 @@
         <v>170</v>
       </c>
       <c r="J31" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>60 Wellb</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="32">
@@ -1820,18 +1796,14 @@
         <v>170</v>
       </c>
       <c r="J32" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>60 Wellb</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="33">
@@ -1865,18 +1837,14 @@
         <v>140</v>
       </c>
       <c r="J33" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>40 Wellb</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="34">
@@ -1913,11 +1881,11 @@
         <v>40</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="35">
@@ -1954,11 +1922,11 @@
         <v>210</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="36">
@@ -1995,11 +1963,11 @@
         <v>210</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="37">
@@ -2036,11 +2004,11 @@
         <v>210</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="38">
@@ -2077,11 +2045,11 @@
         <v>210</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="39">
@@ -2118,11 +2086,11 @@
         <v>210</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="40">
@@ -2163,11 +2131,11 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="41">
@@ -2208,11 +2176,11 @@
         <v>50</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="42">
@@ -2253,11 +2221,11 @@
         <v>50</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="43">
@@ -2298,11 +2266,11 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="44">
@@ -2343,11 +2311,11 @@
         <v>40</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="45">
@@ -2388,11 +2356,11 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="46">
@@ -2433,11 +2401,11 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="47">
@@ -2478,11 +2446,11 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="48">
@@ -2523,11 +2491,11 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="49">
@@ -2568,11 +2536,11 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="50">
@@ -2613,11 +2581,11 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="51">
@@ -2658,11 +2626,11 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="52">
@@ -2699,11 +2667,11 @@
         <v>40</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="53">
@@ -2740,11 +2708,11 @@
         <v>160</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="54">
@@ -2781,11 +2749,11 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="55">
@@ -2822,11 +2790,11 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="56">
@@ -2863,11 +2831,11 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="57">
@@ -2904,11 +2872,11 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="58">
@@ -2945,11 +2913,11 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="59">
@@ -2986,11 +2954,11 @@
         <v>30</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="60">
@@ -3027,11 +2995,11 @@
         <v>30</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="61">
@@ -3068,11 +3036,11 @@
         <v>30</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="62">
@@ -3109,11 +3077,11 @@
         <v>30</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="63">
@@ -3150,11 +3118,11 @@
         <v>30</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="64">
@@ -3191,11 +3159,11 @@
         <v>30</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="65">
@@ -3232,11 +3200,11 @@
         <v>40</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="66">
@@ -3273,11 +3241,11 @@
         <v>30</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="67">
@@ -3311,18 +3279,14 @@
         <v>180</v>
       </c>
       <c r="J67" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>30 Wellb</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="68">
@@ -3356,18 +3320,14 @@
         <v>180</v>
       </c>
       <c r="J68" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>30 Wellb</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="69">
@@ -3401,18 +3361,14 @@
         <v>180</v>
       </c>
       <c r="J69" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>30 Wellb</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="70">
@@ -3446,18 +3402,14 @@
         <v>180</v>
       </c>
       <c r="J70" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>30 Wellb</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="71">
@@ -3494,11 +3446,11 @@
         <v>30</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="72">
@@ -3535,11 +3487,11 @@
         <v>30</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="73">
@@ -3576,11 +3528,11 @@
         <v>30</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="74">
@@ -3617,11 +3569,11 @@
         <v>70</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="75">
@@ -3658,11 +3610,11 @@
         <v>210</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="76">
@@ -3699,11 +3651,11 @@
         <v>210</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="77">
@@ -3740,11 +3692,11 @@
         <v>210</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="78">
@@ -3785,11 +3737,11 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="79">
@@ -3830,11 +3782,11 @@
         <v>50</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="80">
@@ -3875,11 +3827,11 @@
         <v>50</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="81">
@@ -3920,11 +3872,11 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="82">
@@ -3965,11 +3917,11 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="83">
@@ -4010,11 +3962,11 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="84">
@@ -4055,11 +4007,11 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="85">
@@ -4100,11 +4052,11 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="86">
@@ -4145,11 +4097,11 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="87">
@@ -4190,11 +4142,11 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="88">
@@ -4235,11 +4187,11 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="89">
@@ -4280,11 +4232,11 @@
         <v>60</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="90">
@@ -4321,11 +4273,11 @@
         <v>100</v>
       </c>
       <c r="K90" t="n">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="91">
@@ -4362,11 +4314,11 @@
         <v>100</v>
       </c>
       <c r="K91" t="n">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="92">
@@ -4403,11 +4355,11 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="93">
@@ -4444,11 +4396,11 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="94">
@@ -4485,11 +4437,11 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="95">
@@ -4526,11 +4478,11 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="96">
@@ -4567,11 +4519,11 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="97">
@@ -4608,11 +4560,11 @@
         <v>80</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="98">
@@ -4649,11 +4601,11 @@
         <v>70</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="99">
@@ -4690,11 +4642,11 @@
         <v>70</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="100">
@@ -4731,11 +4683,11 @@
         <v>70</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="101">
@@ -4772,11 +4724,11 @@
         <v>70</v>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="102">
@@ -4813,11 +4765,11 @@
         <v>70</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="103">
@@ -4854,11 +4806,11 @@
         <v>50</v>
       </c>
       <c r="K103" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="104">
@@ -4895,11 +4847,11 @@
         <v>30</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="105">
@@ -4936,11 +4888,11 @@
         <v>30</v>
       </c>
       <c r="K105" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="106">
@@ -4977,11 +4929,11 @@
         <v>30</v>
       </c>
       <c r="K106" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="107">
@@ -5018,11 +4970,11 @@
         <v>30</v>
       </c>
       <c r="K107" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="108">
@@ -5059,11 +5011,11 @@
         <v>30</v>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="109">
@@ -5100,11 +5052,11 @@
         <v>30</v>
       </c>
       <c r="K109" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="110">
@@ -5141,11 +5093,11 @@
         <v>30</v>
       </c>
       <c r="K110" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="111">
@@ -5182,11 +5134,11 @@
         <v>70</v>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="112">
@@ -5223,11 +5175,11 @@
         <v>210</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="113">
@@ -5264,11 +5216,11 @@
         <v>110</v>
       </c>
       <c r="K113" t="n">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="114">
@@ -5305,11 +5257,11 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
     <row r="115">
@@ -5346,11 +5298,11 @@
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="n">
-        <v>210</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -6104,7 +6056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7451,10 +7403,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="B47" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -7480,10 +7432,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="B48" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7509,10 +7461,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="B49" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7538,10 +7490,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="B50" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7567,10 +7519,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="B51" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7596,10 +7548,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="B52" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7625,10 +7577,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="B53" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7654,10 +7606,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="B54" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7683,10 +7635,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="B55" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7712,10 +7664,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>4</v>
+        <v>4.6667</v>
       </c>
       <c r="B56" t="n">
-        <v>152</v>
+        <v>177.33</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7741,10 +7693,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>4</v>
+        <v>4.6667</v>
       </c>
       <c r="B57" t="n">
-        <v>152</v>
+        <v>177.33</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7770,10 +7722,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>4</v>
+        <v>4.6667</v>
       </c>
       <c r="B58" t="n">
-        <v>152</v>
+        <v>177.33</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7799,10 +7751,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>4</v>
+        <v>4.6667</v>
       </c>
       <c r="B59" t="n">
-        <v>152</v>
+        <v>177.33</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7828,10 +7780,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>4</v>
+        <v>4.6667</v>
       </c>
       <c r="B60" t="n">
-        <v>152</v>
+        <v>177.33</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7857,10 +7809,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>4</v>
+        <v>4.6667</v>
       </c>
       <c r="B61" t="n">
-        <v>152</v>
+        <v>177.33</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7886,10 +7838,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>4</v>
+        <v>4.6667</v>
       </c>
       <c r="B62" t="n">
-        <v>152</v>
+        <v>177.33</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7915,10 +7867,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4</v>
+        <v>4.6667</v>
       </c>
       <c r="B63" t="n">
-        <v>152</v>
+        <v>177.33</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7944,10 +7896,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>4</v>
+        <v>4.6667</v>
       </c>
       <c r="B64" t="n">
-        <v>152</v>
+        <v>177.33</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7968,267 +7920,6 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>4.6667</v>
-      </c>
-      <c r="B65" t="n">
-        <v>177.33</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>E3</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Entry Level Award</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>40</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>4.6667</v>
-      </c>
-      <c r="B66" t="n">
-        <v>177.33</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>E3</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Entry Level Extended Award</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>90</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>4.6667</v>
-      </c>
-      <c r="B67" t="n">
-        <v>177.33</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>E3</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Entry Level Certificate</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>140</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>4.6667</v>
-      </c>
-      <c r="B68" t="n">
-        <v>177.33</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Level 1 Award</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>36</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>4.6667</v>
-      </c>
-      <c r="B69" t="n">
-        <v>177.33</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Level 1 Extended Award</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>81</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>4.6667</v>
-      </c>
-      <c r="B70" t="n">
-        <v>177.33</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Level 1 Certificate</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>135</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>4.6667</v>
-      </c>
-      <c r="B71" t="n">
-        <v>177.33</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Level 2 Award</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>32</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>4.6667</v>
-      </c>
-      <c r="B72" t="n">
-        <v>177.33</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Level 2 Extended Award</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>72</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>4.6667</v>
-      </c>
-      <c r="B73" t="n">
-        <v>177.33</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Level 2 Certificate</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>120</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G73" t="n">
         <v>0</v>
       </c>
     </row>

--- a/_passpq/inputs/PEQ_L2K_YearPlan_2026-27.xlsx
+++ b/_passpq/inputs/PEQ_L2K_YearPlan_2026-27.xlsx
@@ -808,7 +808,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aut2</t>
+          <t>Aut1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spr1</t>
+          <t>Aut2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Spr2</t>
+          <t>Spr1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sum1</t>
+          <t>Spr2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sum2</t>
+          <t>Sum1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Aut2</t>
+          <t>Aut1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Spr1</t>
+          <t>Aut2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Spr2</t>
+          <t>Spr1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sum1</t>
+          <t>Spr2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sum2</t>
+          <t>Sum1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Aut2</t>
+          <t>Aut1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Spr1</t>
+          <t>Aut2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Spr2</t>
+          <t>Spr1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -4819,7 +4819,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Sum1</t>
+          <t>Spr2</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Sum2</t>
+          <t>Sum1</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>

--- a/_passpq/inputs/PEQ_L2K_YearPlan_2026-27.xlsx
+++ b/_passpq/inputs/PEQ_L2K_YearPlan_2026-27.xlsx
@@ -525,11 +525,11 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3">
@@ -570,11 +570,11 @@
         <v>50</v>
       </c>
       <c r="K3" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4">
@@ -615,11 +615,11 @@
         <v>50</v>
       </c>
       <c r="K4" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5">
@@ -660,11 +660,11 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6">
@@ -705,11 +705,11 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7">
@@ -750,11 +750,11 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8">
@@ -795,11 +795,11 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9">
@@ -840,11 +840,11 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -885,11 +885,11 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11">
@@ -930,11 +930,11 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="12">
@@ -975,11 +975,11 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13">
@@ -1020,11 +1020,11 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14">
@@ -1061,11 +1061,11 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="15">
@@ -1102,11 +1102,11 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="16">
@@ -1143,11 +1143,11 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="17">
@@ -1184,11 +1184,11 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18">
@@ -1225,11 +1225,11 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="19">
@@ -1266,11 +1266,11 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20">
@@ -1307,11 +1307,11 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21">
@@ -1348,11 +1348,11 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22">
@@ -1389,11 +1389,11 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="23">
@@ -1430,11 +1430,11 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="24">
@@ -1471,11 +1471,11 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="25">
@@ -1512,11 +1512,11 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="26">
@@ -1553,11 +1553,11 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="27">
@@ -1594,11 +1594,11 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="28">
@@ -1635,11 +1635,11 @@
         <v>100</v>
       </c>
       <c r="K28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="29">
@@ -1676,11 +1676,11 @@
         <v>100</v>
       </c>
       <c r="K29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="30">
@@ -1717,11 +1717,11 @@
         <v>100</v>
       </c>
       <c r="K30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="31">
@@ -1758,11 +1758,11 @@
         <v>100</v>
       </c>
       <c r="K31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="32">
@@ -1799,11 +1799,11 @@
         <v>100</v>
       </c>
       <c r="K32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="33">
@@ -1840,11 +1840,11 @@
         <v>110</v>
       </c>
       <c r="K33" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="34">
@@ -1881,11 +1881,11 @@
         <v>40</v>
       </c>
       <c r="K34" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35">
@@ -1922,11 +1922,11 @@
         <v>210</v>
       </c>
       <c r="K35" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="36">
@@ -1963,11 +1963,11 @@
         <v>210</v>
       </c>
       <c r="K36" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="37">
@@ -2004,11 +2004,11 @@
         <v>210</v>
       </c>
       <c r="K37" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="38">
@@ -2045,11 +2045,11 @@
         <v>210</v>
       </c>
       <c r="K38" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="39">
@@ -2086,11 +2086,11 @@
         <v>210</v>
       </c>
       <c r="K39" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="40">
@@ -2131,11 +2131,11 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="41">
@@ -2176,11 +2176,11 @@
         <v>50</v>
       </c>
       <c r="K41" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="42">
@@ -2221,11 +2221,11 @@
         <v>50</v>
       </c>
       <c r="K42" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="43">
@@ -2266,11 +2266,11 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="44">
@@ -2311,11 +2311,11 @@
         <v>40</v>
       </c>
       <c r="K44" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="45">
@@ -2356,11 +2356,11 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="46">
@@ -2401,11 +2401,11 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="47">
@@ -2446,11 +2446,11 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="48">
@@ -2491,11 +2491,11 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="49">
@@ -2536,11 +2536,11 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50">
@@ -2581,11 +2581,11 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="51">
@@ -2626,11 +2626,11 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52">
@@ -2667,11 +2667,11 @@
         <v>40</v>
       </c>
       <c r="K52" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="53">
@@ -2708,11 +2708,11 @@
         <v>160</v>
       </c>
       <c r="K53" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54">
@@ -2749,11 +2749,11 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55">
@@ -2790,11 +2790,11 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56">
@@ -2831,11 +2831,11 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57">
@@ -2872,11 +2872,11 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58">
@@ -2913,11 +2913,11 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59">
@@ -2954,11 +2954,11 @@
         <v>30</v>
       </c>
       <c r="K59" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60">
@@ -2995,11 +2995,11 @@
         <v>30</v>
       </c>
       <c r="K60" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61">
@@ -3036,11 +3036,11 @@
         <v>30</v>
       </c>
       <c r="K61" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="62">
@@ -3077,11 +3077,11 @@
         <v>30</v>
       </c>
       <c r="K62" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="63">
@@ -3118,11 +3118,11 @@
         <v>30</v>
       </c>
       <c r="K63" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="64">
@@ -3159,11 +3159,11 @@
         <v>30</v>
       </c>
       <c r="K64" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="65">
@@ -3200,11 +3200,11 @@
         <v>40</v>
       </c>
       <c r="K65" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="66">
@@ -3241,11 +3241,11 @@
         <v>30</v>
       </c>
       <c r="K66" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="67">
@@ -3282,11 +3282,11 @@
         <v>60</v>
       </c>
       <c r="K67" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="68">
@@ -3323,11 +3323,11 @@
         <v>60</v>
       </c>
       <c r="K68" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="69">
@@ -3364,11 +3364,11 @@
         <v>60</v>
       </c>
       <c r="K69" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="70">
@@ -3405,11 +3405,11 @@
         <v>60</v>
       </c>
       <c r="K70" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="71">
@@ -3446,11 +3446,11 @@
         <v>30</v>
       </c>
       <c r="K71" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="72">
@@ -3487,11 +3487,11 @@
         <v>30</v>
       </c>
       <c r="K72" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="73">
@@ -3528,11 +3528,11 @@
         <v>30</v>
       </c>
       <c r="K73" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="74">
@@ -3569,11 +3569,11 @@
         <v>70</v>
       </c>
       <c r="K74" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="75">
@@ -3610,11 +3610,11 @@
         <v>210</v>
       </c>
       <c r="K75" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="76">
@@ -3651,11 +3651,11 @@
         <v>210</v>
       </c>
       <c r="K76" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="77">
@@ -3692,11 +3692,11 @@
         <v>210</v>
       </c>
       <c r="K77" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="78">
@@ -3737,11 +3737,11 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="79">
@@ -3782,11 +3782,11 @@
         <v>50</v>
       </c>
       <c r="K79" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="80">
@@ -3827,11 +3827,11 @@
         <v>50</v>
       </c>
       <c r="K80" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="81">
@@ -3872,11 +3872,11 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="82">
@@ -3917,11 +3917,11 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="83">
@@ -3962,11 +3962,11 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="84">
@@ -4007,11 +4007,11 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="85">
@@ -4052,11 +4052,11 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="86">
@@ -4097,11 +4097,11 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="87">
@@ -4142,11 +4142,11 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="88">
@@ -4187,11 +4187,11 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="89">
@@ -4232,11 +4232,11 @@
         <v>60</v>
       </c>
       <c r="K89" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="90">
@@ -4273,11 +4273,11 @@
         <v>100</v>
       </c>
       <c r="K90" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="91">
@@ -4314,11 +4314,11 @@
         <v>100</v>
       </c>
       <c r="K91" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="92">
@@ -4355,11 +4355,11 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="93">
@@ -4396,11 +4396,11 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="94">
@@ -4437,11 +4437,11 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="95">
@@ -4478,11 +4478,11 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="96">
@@ -4519,11 +4519,11 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="97">
@@ -4560,11 +4560,11 @@
         <v>80</v>
       </c>
       <c r="K97" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="98">
@@ -4601,11 +4601,11 @@
         <v>70</v>
       </c>
       <c r="K98" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="99">
@@ -4642,11 +4642,11 @@
         <v>70</v>
       </c>
       <c r="K99" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="100">
@@ -4683,11 +4683,11 @@
         <v>70</v>
       </c>
       <c r="K100" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="101">
@@ -4724,11 +4724,11 @@
         <v>70</v>
       </c>
       <c r="K101" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="102">
@@ -4765,11 +4765,11 @@
         <v>70</v>
       </c>
       <c r="K102" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="103">
@@ -4806,11 +4806,11 @@
         <v>50</v>
       </c>
       <c r="K103" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="104">
@@ -4847,11 +4847,11 @@
         <v>30</v>
       </c>
       <c r="K104" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="105">
@@ -4888,11 +4888,11 @@
         <v>30</v>
       </c>
       <c r="K105" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="106">
@@ -4929,11 +4929,11 @@
         <v>30</v>
       </c>
       <c r="K106" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="107">
@@ -4970,11 +4970,11 @@
         <v>30</v>
       </c>
       <c r="K107" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="108">
@@ -5011,11 +5011,11 @@
         <v>30</v>
       </c>
       <c r="K108" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="109">
@@ -5052,11 +5052,11 @@
         <v>30</v>
       </c>
       <c r="K109" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="110">
@@ -5093,11 +5093,11 @@
         <v>30</v>
       </c>
       <c r="K110" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="111">
@@ -5134,11 +5134,11 @@
         <v>70</v>
       </c>
       <c r="K111" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="112">
@@ -5175,11 +5175,11 @@
         <v>210</v>
       </c>
       <c r="K112" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="113">
@@ -5216,11 +5216,11 @@
         <v>110</v>
       </c>
       <c r="K113" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="114">
@@ -5257,11 +5257,11 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="115">
@@ -5298,11 +5298,11 @@
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -6056,7 +6056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7920,6 +7920,267 @@
         </is>
       </c>
       <c r="G64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>5.3333</v>
+      </c>
+      <c r="B65" t="n">
+        <v>202.67</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Entry Level Award</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>40</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>5.3333</v>
+      </c>
+      <c r="B66" t="n">
+        <v>202.67</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Entry Level Extended Award</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>90</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>5.3333</v>
+      </c>
+      <c r="B67" t="n">
+        <v>202.67</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Entry Level Certificate</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>140</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>5.3333</v>
+      </c>
+      <c r="B68" t="n">
+        <v>202.67</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Level 1 Award</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>36</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>5.3333</v>
+      </c>
+      <c r="B69" t="n">
+        <v>202.67</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Level 1 Extended Award</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>81</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>5.3333</v>
+      </c>
+      <c r="B70" t="n">
+        <v>202.67</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Level 1 Certificate</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>135</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>5.3333</v>
+      </c>
+      <c r="B71" t="n">
+        <v>202.67</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Level 2 Award</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>32</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>5.3333</v>
+      </c>
+      <c r="B72" t="n">
+        <v>202.67</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Level 2 Extended Award</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>72</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>5.3333</v>
+      </c>
+      <c r="B73" t="n">
+        <v>202.67</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Level 2 Certificate</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>120</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
         <v>0</v>
       </c>
     </row>
